--- a/results/Int Task Remove ACC 1.0/Linea_fi_explain.xlsx
+++ b/results/Int Task Remove ACC 1.0/Linea_fi_explain.xlsx
@@ -1166,13 +1166,13 @@
         <v>0.02703871905781815</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02331161524344078</v>
+        <v>0.02330555463738018</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0004655594384187334</v>
+        <v>-0.0004657397954995191</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.001046712829188895</v>
+        <v>-0.001035438872029931</v>
       </c>
       <c r="K3" t="n">
         <v>0.001900080022703401</v>
@@ -1196,7 +1196,7 @@
         <v>-0.002392405468591062</v>
       </c>
       <c r="R3" t="n">
-        <v>0.00541219371086249</v>
+        <v>0.005412714150718109</v>
       </c>
       <c r="S3" t="n">
         <v>0.3679365138731313</v>
@@ -1208,7 +1208,7 @@
         <v>0.3205823683776614</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.000465836607874015</v>
+        <v>-0.0004602118448358461</v>
       </c>
       <c r="W3" t="n">
         <v>0.0007385757408734984</v>
@@ -1250,7 +1250,7 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.02113938314099671</v>
+        <v>0.02113447154964111</v>
       </c>
       <c r="AK3" t="n">
         <v>0.02112231947930739</v>
@@ -1364,7 +1364,7 @@
         <v>0.02112958506677542</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.007496487417915488</v>
+        <v>0.007490850439336008</v>
       </c>
       <c r="BW3" t="n">
         <v>0.02506958548393936</v>
@@ -1406,7 +1406,7 @@
         <v>0.0360327865630924</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.02506394850535988</v>
+        <v>0.02506958548393936</v>
       </c>
       <c r="CK3" t="n">
         <v>-0.001226165252456748</v>
@@ -1437,13 +1437,13 @@
         <v>0.03961628277671309</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03242287255391358</v>
+        <v>0.03242775727420202</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000968002067060527</v>
+        <v>0.0009801908451568691</v>
       </c>
       <c r="J4" t="n">
-        <v>0.009511094536483137</v>
+        <v>0.00951246559011475</v>
       </c>
       <c r="K4" t="n">
         <v>0.01718075907548558</v>
@@ -1467,7 +1467,7 @@
         <v>0.00410335571326876</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0139672903598693</v>
+        <v>0.01396342892188373</v>
       </c>
       <c r="S4" t="n">
         <v>0.1147570065159508</v>
@@ -1479,7 +1479,7 @@
         <v>0.1224855902362463</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0009855098461578312</v>
+        <v>0.0009696930082503889</v>
       </c>
       <c r="W4" t="n">
         <v>0.003852844820679295</v>
@@ -1521,7 +1521,7 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.03198907908402556</v>
+        <v>0.03199213605443739</v>
       </c>
       <c r="AK4" t="n">
         <v>0.04298168578885574</v>
@@ -1635,7 +1635,7 @@
         <v>0.02662785962562696</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.02115037802451773</v>
+        <v>0.02115404076154644</v>
       </c>
       <c r="BW4" t="n">
         <v>0.03673200610937404</v>
@@ -1677,7 +1677,7 @@
         <v>0.04660647939552064</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.03673130621274071</v>
+        <v>0.03673200610937404</v>
       </c>
       <c r="CK4" t="n">
         <v>0.003018989349455335</v>
@@ -1711,7 +1711,7 @@
         <v>-0.002554027504911627</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.00255962769051783</v>
+        <v>-0.002617801047120505</v>
       </c>
       <c r="J5" t="n">
         <v>-0.01983711460151256</v>
@@ -1738,7 +1738,7 @@
         <v>-0.01213163064833007</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.01387878787878786</v>
+        <v>-0.0138181818181818</v>
       </c>
       <c r="S5" t="n">
         <v>0.2347878787878788</v>
@@ -1750,7 +1750,7 @@
         <v>0.1177799607072691</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.002617801047120505</v>
+        <v>-0.00255962769051783</v>
       </c>
       <c r="W5" t="n">
         <v>-0.003090909090909111</v>
@@ -1792,7 +1792,7 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.003241650294695464</v>
+        <v>0.003192534381139467</v>
       </c>
       <c r="AK5" t="n">
         <v>-0.01527995813710097</v>
@@ -1906,7 +1906,7 @@
         <v>-0.002152414194299079</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.004847801578353983</v>
+        <v>-0.004904171364148791</v>
       </c>
       <c r="BW5" t="n">
         <v>-0.003980634749865541</v>
@@ -1979,10 +1979,10 @@
         <v>0.004072580645161298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0007640600924499253</v>
+        <v>0.0007186055469953795</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0008791124321000293</v>
+        <v>-0.0008650199856513246</v>
       </c>
       <c r="J6" t="n">
         <v>-0.003821128947857055</v>
@@ -2292,7 +2292,7 @@
         <v>0.3064946365851343</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.0002144787533781833</v>
+        <v>-0.000187740785463747</v>
       </c>
       <c r="W7" t="n">
         <v>-0.0001389038834681944</v>
@@ -2527,7 +2527,7 @@
         <v>0.0001708362867840929</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00179072038777591</v>
+        <v>0.001818905280673319</v>
       </c>
       <c r="K8" t="n">
         <v>0.007308451916746873</v>
@@ -2563,7 +2563,7 @@
         <v>0.4025405329402163</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001846867022965576</v>
+        <v>0.0001708362867840929</v>
       </c>
       <c r="W8" t="n">
         <v>0.001427483267290439</v>
@@ -2761,7 +2761,7 @@
         <v>0.05349578583098712</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.02804722401413166</v>
+        <v>0.02808950135347777</v>
       </c>
       <c r="CK8" t="n">
         <v>0.0004030478971378871</v>
